--- a/upload/acordos_cooperacao_tecnica.xlsx
+++ b/upload/acordos_cooperacao_tecnica.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5972" uniqueCount="2823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5979" uniqueCount="2827">
   <si>
     <t>ano</t>
   </si>
@@ -8577,6 +8577,21 @@
   <si>
     <t>MUNICÍPIO DE
 INHAÚMA</t>
+  </si>
+  <si>
+    <t>1190.01.0013435/2025-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SECRETARIA DE ESTADO DE
+FAZENDA DE MINAS GERAIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGÊNCIA DE
+DESENVOLVIMENTO DA REGIÃO METROPOLITANA DO VALE
+DO AÇO - AGÊNCIA RMVA </t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/apps/files/files/616373?dir=/FTP_DTA/Acordos%20de%20Coopera%C3%A7%C3%A3o%20T%C3%A9cnica/AGENCIA%20ARMVA</t>
   </si>
 </sst>
 </file>
@@ -9506,7 +9521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N943"/>
+  <dimension ref="A1:N944"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -10555,7 +10570,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -13366,7 +13381,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2022</v>
       </c>
@@ -17795,7 +17810,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2023</v>
       </c>
@@ -28240,7 +28255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="580" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>2024</v>
       </c>
@@ -32818,7 +32833,7 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>2025</v>
       </c>
@@ -34915,7 +34930,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="788" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A788">
         <v>2025</v>
       </c>
@@ -39375,7 +39390,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="929" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B929">
         <v>1</v>
       </c>
@@ -39404,7 +39419,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="930" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B930">
         <v>1</v>
       </c>
@@ -39433,7 +39448,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="931" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B931">
         <v>1</v>
       </c>
@@ -39462,7 +39477,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="932" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B932">
         <v>1</v>
       </c>
@@ -39491,7 +39506,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="933" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B933">
         <v>1</v>
       </c>
@@ -39520,7 +39535,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="934" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B934">
         <v>1</v>
       </c>
@@ -39549,7 +39564,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="935" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B935">
         <v>1</v>
       </c>
@@ -39578,7 +39593,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="936" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B936">
         <v>1</v>
       </c>
@@ -39607,7 +39622,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="937" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B937">
         <v>1</v>
       </c>
@@ -39636,7 +39651,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="938" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B938">
         <v>1</v>
       </c>
@@ -39665,7 +39680,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="939" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B939">
         <v>1</v>
       </c>
@@ -39694,7 +39709,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="940" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B940">
         <v>1</v>
       </c>
@@ -39723,7 +39738,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="941" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B941">
         <v>1</v>
       </c>
@@ -39752,7 +39767,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="942" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B942">
         <v>1</v>
       </c>
@@ -39781,7 +39796,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="943" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B943">
         <v>1</v>
       </c>
@@ -39808,6 +39823,38 @@
       </c>
       <c r="J943" s="4" t="s">
         <v>2307</v>
+      </c>
+    </row>
+    <row r="944" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A944">
+        <v>2025</v>
+      </c>
+      <c r="B944" t="s">
+        <v>11</v>
+      </c>
+      <c r="C944" s="24" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D944" s="6" t="s">
+        <v>2825</v>
+      </c>
+      <c r="E944" s="8" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F944" s="6" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G944" s="1">
+        <v>45968</v>
+      </c>
+      <c r="H944" s="1">
+        <v>47793</v>
+      </c>
+      <c r="I944" t="s">
+        <v>16</v>
+      </c>
+      <c r="J944" s="4" t="s">
+        <v>2826</v>
       </c>
     </row>
   </sheetData>
@@ -39933,9 +39980,10 @@
     <hyperlink ref="J670" r:id="rId114"/>
     <hyperlink ref="J671" r:id="rId115"/>
     <hyperlink ref="J672" r:id="rId116"/>
+    <hyperlink ref="J944" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId117"/>
-  <drawing r:id="rId118"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId118"/>
+  <drawing r:id="rId119"/>
 </worksheet>
 </file>
--- a/upload/acordos_cooperacao_tecnica.xlsx
+++ b/upload/acordos_cooperacao_tecnica.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11467" uniqueCount="5229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11469" uniqueCount="5231">
   <si>
     <t>ano</t>
   </si>
@@ -15986,6 +15986,12 @@
   </si>
   <si>
     <t>numero/sei</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/TT3WpHtBiPCs3WR</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/dW6oGmr8KECZ5xB</t>
   </si>
 </sst>
 </file>
@@ -19967,7 +19973,7 @@
         <v>2686</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2026</v>
       </c>
@@ -19999,7 +20005,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2026</v>
       </c>
@@ -20031,7 +20037,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
         <v>2026</v>
       </c>
@@ -20063,7 +20069,7 @@
         <v>4629</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <v>2026</v>
       </c>
@@ -30047,7 +30053,7 @@
         <v>2686</v>
       </c>
     </row>
-    <row r="405" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2025</v>
       </c>
@@ -30079,7 +30085,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="406" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2025</v>
       </c>
@@ -30175,7 +30181,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="12">
         <v>2025</v>
       </c>
@@ -30207,7 +30213,7 @@
         <v>4633</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="12">
         <v>2025</v>
       </c>
@@ -39126,7 +39132,9 @@
       <c r="I688" t="s">
         <v>14</v>
       </c>
-      <c r="J688" s="3"/>
+      <c r="J688" s="3" t="s">
+        <v>5229</v>
+      </c>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A689">
@@ -40536,7 +40544,7 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="733" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A733" s="6">
         <v>2024</v>
       </c>
@@ -40600,7 +40608,7 @@
         <v>3523</v>
       </c>
     </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>2024</v>
       </c>
@@ -44575,7 +44583,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="858" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A858">
         <v>2024</v>
       </c>
@@ -44607,7 +44615,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="859" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A859">
         <v>2024</v>
       </c>
@@ -44671,7 +44679,7 @@
         <v>4589</v>
       </c>
     </row>
-    <row r="861" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="12">
         <v>2024</v>
       </c>
@@ -44703,7 +44711,7 @@
         <v>4626</v>
       </c>
     </row>
-    <row r="862" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="12">
         <v>2024</v>
       </c>
@@ -54680,7 +54688,9 @@
       <c r="I1173" t="s">
         <v>14</v>
       </c>
-      <c r="J1173" s="3"/>
+      <c r="J1173" s="3" t="s">
+        <v>5230</v>
+      </c>
     </row>
     <row r="1174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1174">
@@ -57572,7 +57582,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="1263" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1263">
         <v>2023</v>
       </c>
@@ -57636,7 +57646,7 @@
         <v>4617</v>
       </c>
     </row>
-    <row r="1265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1265" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1265" s="12">
         <v>2023</v>
       </c>
